--- a/results/Compact/Results_Analysis_Compact.xlsx
+++ b/results/Compact/Results_Analysis_Compact.xlsx
@@ -1182,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>0.21284</v>
+        <v>0.21412</v>
       </c>
       <c r="E21">
         <v>0.204</v>
@@ -1197,13 +1197,13 @@
         <v>0.104</v>
       </c>
       <c r="I21">
-        <v>0.0293877525510203</v>
+        <v>0.02892133007545354</v>
       </c>
       <c r="J21">
-        <v>0.00086364</v>
+        <v>0.0008364433333333336</v>
       </c>
       <c r="K21">
-        <v>0.189</v>
+        <v>0.197</v>
       </c>
       <c r="L21">
         <v>0.239</v>
@@ -1256,31 +1256,31 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0.08295999999999999</v>
+        <v>0.10672</v>
       </c>
       <c r="E23">
-        <v>0.078</v>
+        <v>0.1063</v>
       </c>
       <c r="F23">
-        <v>0.045</v>
+        <v>0.058</v>
       </c>
       <c r="G23">
-        <v>0.146</v>
+        <v>0.163</v>
       </c>
       <c r="H23">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="I23">
-        <v>0.02469730079718565</v>
+        <v>0.02486917435970348</v>
       </c>
       <c r="J23">
-        <v>0.0006099566666666667</v>
+        <v>0.0006184758333333331</v>
       </c>
       <c r="K23">
-        <v>0.066</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L23">
-        <v>0.097</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1328,10 +1328,10 @@
         <v>17</v>
       </c>
       <c r="D25">
-        <v>0.14504</v>
+        <v>0.1482</v>
       </c>
       <c r="E25">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="F25">
         <v>0.099</v>
@@ -1343,13 +1343,13 @@
         <v>0.133</v>
       </c>
       <c r="I25">
-        <v>0.03616683563708608</v>
+        <v>0.03545302055772775</v>
       </c>
       <c r="J25">
-        <v>0.00130804</v>
+        <v>0.001256916666666666</v>
       </c>
       <c r="K25">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="L25">
         <v>0.168</v>
@@ -1366,10 +1366,10 @@
         <v>17</v>
       </c>
       <c r="D26">
-        <v>0.12432</v>
+        <v>0.12744</v>
       </c>
       <c r="E26">
-        <v>0.126</v>
+        <v>0.13</v>
       </c>
       <c r="F26">
         <v>0.075</v>
@@ -1381,13 +1381,13 @@
         <v>0.09799999999999999</v>
       </c>
       <c r="I26">
-        <v>0.0286599604558927</v>
+        <v>0.02667720625053031</v>
       </c>
       <c r="J26">
-        <v>0.0008213933333333334</v>
+        <v>0.0007116733333333334</v>
       </c>
       <c r="K26">
-        <v>0.107</v>
+        <v>0.11</v>
       </c>
       <c r="L26">
         <v>0.141</v>

--- a/results/Compact/Results_Analysis_Compact.xlsx
+++ b/results/Compact/Results_Analysis_Compact.xlsx
@@ -816,31 +816,31 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <v>546.4576000000001</v>
+        <v>597.2976</v>
       </c>
       <c r="E11">
-        <v>549.66</v>
+        <v>595.0599999999999</v>
       </c>
       <c r="F11">
-        <v>466.8</v>
+        <v>526.8</v>
       </c>
       <c r="G11">
-        <v>620.04</v>
+        <v>664.9</v>
       </c>
       <c r="H11">
-        <v>153.24</v>
+        <v>138.1</v>
       </c>
       <c r="I11">
-        <v>42.08653162236106</v>
+        <v>40.26645018705607</v>
       </c>
       <c r="J11">
-        <v>1771.276143999998</v>
+        <v>1621.387010666667</v>
       </c>
       <c r="K11">
-        <v>510.76</v>
+        <v>572.08</v>
       </c>
       <c r="L11">
-        <v>567.98</v>
+        <v>627.76</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -888,31 +888,31 @@
         <v>16</v>
       </c>
       <c r="D13">
-        <v>417.224</v>
+        <v>424.224</v>
       </c>
       <c r="E13">
-        <v>418.52</v>
+        <v>427.46</v>
       </c>
       <c r="F13">
         <v>343.26</v>
       </c>
       <c r="G13">
-        <v>486.42</v>
+        <v>492.38</v>
       </c>
       <c r="H13">
-        <v>143.16</v>
+        <v>149.12</v>
       </c>
       <c r="I13">
-        <v>39.33858665483549</v>
+        <v>43.52634527884618</v>
       </c>
       <c r="J13">
-        <v>1547.524400000001</v>
+        <v>1894.542733333335</v>
       </c>
       <c r="K13">
         <v>386.78</v>
       </c>
       <c r="L13">
-        <v>439.94</v>
+        <v>463.96</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -926,31 +926,31 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>1139.2072</v>
+        <v>1208.4072</v>
       </c>
       <c r="E14">
-        <v>1151.54</v>
+        <v>1201.38</v>
       </c>
       <c r="F14">
-        <v>952.0599999999999</v>
+        <v>982.0599999999999</v>
       </c>
       <c r="G14">
-        <v>1270.02</v>
+        <v>1451.54</v>
       </c>
       <c r="H14">
-        <v>317.96</v>
+        <v>469.48</v>
       </c>
       <c r="I14">
-        <v>85.58027223607091</v>
+        <v>108.3738667576276</v>
       </c>
       <c r="J14">
-        <v>7323.982996000009</v>
+        <v>11744.89499600002</v>
       </c>
       <c r="K14">
-        <v>1077.62</v>
+        <v>1151.48</v>
       </c>
       <c r="L14">
-        <v>1214.96</v>
+        <v>1287.18</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -998,10 +998,10 @@
         <v>16</v>
       </c>
       <c r="D16">
-        <v>889.02</v>
+        <v>893.8200000000001</v>
       </c>
       <c r="E16">
-        <v>886.9400000000001</v>
+        <v>896.64</v>
       </c>
       <c r="F16">
         <v>751.16</v>
@@ -1013,16 +1013,16 @@
         <v>292.2200000000001</v>
       </c>
       <c r="I16">
-        <v>83.64061473550593</v>
+        <v>83.14877690020465</v>
       </c>
       <c r="J16">
-        <v>6995.752433333332</v>
+        <v>6913.719100000007</v>
       </c>
       <c r="K16">
-        <v>803.36</v>
+        <v>829.9400000000001</v>
       </c>
       <c r="L16">
-        <v>951.7</v>
+        <v>962.76</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1036,31 +1036,31 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>1787.2464</v>
+        <v>1815.6864</v>
       </c>
       <c r="E17">
-        <v>1809.04</v>
+        <v>1830.42</v>
       </c>
       <c r="F17">
-        <v>1538.06</v>
+        <v>1567.16</v>
       </c>
       <c r="G17">
-        <v>1981.12</v>
+        <v>2001.68</v>
       </c>
       <c r="H17">
-        <v>443.0599999999999</v>
+        <v>434.52</v>
       </c>
       <c r="I17">
-        <v>129.260691849198</v>
+        <v>130.9182210032915</v>
       </c>
       <c r="J17">
-        <v>16708.32645733333</v>
+        <v>17139.58059066668</v>
       </c>
       <c r="K17">
-        <v>1695.46</v>
+        <v>1698.18</v>
       </c>
       <c r="L17">
-        <v>1907.74</v>
+        <v>1929.04</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1108,7 +1108,7 @@
         <v>16</v>
       </c>
       <c r="D19">
-        <v>1429.1808</v>
+        <v>1435.5808</v>
       </c>
       <c r="E19">
         <v>1447.16</v>
@@ -1117,22 +1117,22 @@
         <v>1155.72</v>
       </c>
       <c r="G19">
-        <v>1627</v>
+        <v>1628.6</v>
       </c>
       <c r="H19">
-        <v>471.28</v>
+        <v>472.8799999999999</v>
       </c>
       <c r="I19">
-        <v>121.2009284177862</v>
+        <v>123.4635751250816</v>
       </c>
       <c r="J19">
-        <v>14689.66504933333</v>
+        <v>15243.25438266667</v>
       </c>
       <c r="K19">
         <v>1360.22</v>
       </c>
       <c r="L19">
-        <v>1528.6</v>
+        <v>1536.74</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1146,31 +1146,31 @@
         <v>17</v>
       </c>
       <c r="D20">
-        <v>0.05884</v>
+        <v>0.13944</v>
       </c>
       <c r="E20">
-        <v>0.057</v>
+        <v>0.135</v>
       </c>
       <c r="F20">
-        <v>0.015</v>
+        <v>0.103</v>
       </c>
       <c r="G20">
-        <v>0.092</v>
+        <v>0.19</v>
       </c>
       <c r="H20">
-        <v>0.077</v>
+        <v>0.08700000000000001</v>
       </c>
       <c r="I20">
-        <v>0.01902121622469674</v>
+        <v>0.02364332181963158</v>
       </c>
       <c r="J20">
-        <v>0.0003618066666666666</v>
+        <v>0.0005590066666666667</v>
       </c>
       <c r="K20">
-        <v>0.044</v>
+        <v>0.12</v>
       </c>
       <c r="L20">
-        <v>0.073</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1182,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>0.21412</v>
+        <v>0.21284</v>
       </c>
       <c r="E21">
         <v>0.204</v>
@@ -1197,13 +1197,13 @@
         <v>0.104</v>
       </c>
       <c r="I21">
-        <v>0.02892133007545354</v>
+        <v>0.0293877525510203</v>
       </c>
       <c r="J21">
-        <v>0.0008364433333333336</v>
+        <v>0.00086364</v>
       </c>
       <c r="K21">
-        <v>0.197</v>
+        <v>0.189</v>
       </c>
       <c r="L21">
         <v>0.239</v>
@@ -1218,31 +1218,31 @@
         <v>17</v>
       </c>
       <c r="D22">
-        <v>0.11504</v>
+        <v>0.1286</v>
       </c>
       <c r="E22">
-        <v>0.116</v>
+        <v>0.12</v>
       </c>
       <c r="F22">
-        <v>0.07099999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G22">
-        <v>0.153</v>
+        <v>0.232</v>
       </c>
       <c r="H22">
-        <v>0.082</v>
+        <v>0.132</v>
       </c>
       <c r="I22">
-        <v>0.01780327685193562</v>
+        <v>0.02827690459249975</v>
       </c>
       <c r="J22">
-        <v>0.0003169566666666666</v>
+        <v>0.0007995833333333332</v>
       </c>
       <c r="K22">
-        <v>0.108</v>
+        <v>0.111</v>
       </c>
       <c r="L22">
-        <v>0.123</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1256,31 +1256,31 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0.10672</v>
+        <v>0.1342</v>
       </c>
       <c r="E23">
-        <v>0.1063</v>
+        <v>0.121</v>
       </c>
       <c r="F23">
-        <v>0.058</v>
+        <v>0.102</v>
       </c>
       <c r="G23">
-        <v>0.163</v>
+        <v>0.253</v>
       </c>
       <c r="H23">
-        <v>0.105</v>
+        <v>0.151</v>
       </c>
       <c r="I23">
-        <v>0.02486917435970348</v>
+        <v>0.03384769809996932</v>
       </c>
       <c r="J23">
-        <v>0.0006184758333333331</v>
+        <v>0.001145666666666667</v>
       </c>
       <c r="K23">
-        <v>0.08799999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="L23">
-        <v>0.122</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1328,28 +1328,28 @@
         <v>17</v>
       </c>
       <c r="D25">
-        <v>0.1482</v>
+        <v>0.1498</v>
       </c>
       <c r="E25">
         <v>0.132</v>
       </c>
       <c r="F25">
-        <v>0.099</v>
+        <v>0.119</v>
       </c>
       <c r="G25">
         <v>0.232</v>
       </c>
       <c r="H25">
-        <v>0.133</v>
+        <v>0.113</v>
       </c>
       <c r="I25">
-        <v>0.03545302055772775</v>
+        <v>0.03192438984016244</v>
       </c>
       <c r="J25">
-        <v>0.001256916666666666</v>
+        <v>0.001019166666666667</v>
       </c>
       <c r="K25">
-        <v>0.124</v>
+        <v>0.128</v>
       </c>
       <c r="L25">
         <v>0.168</v>
@@ -1366,31 +1366,31 @@
         <v>17</v>
       </c>
       <c r="D26">
-        <v>0.12744</v>
+        <v>0.13828</v>
       </c>
       <c r="E26">
-        <v>0.13</v>
+        <v>0.135</v>
       </c>
       <c r="F26">
-        <v>0.075</v>
+        <v>0.103</v>
       </c>
       <c r="G26">
-        <v>0.173</v>
+        <v>0.177</v>
       </c>
       <c r="H26">
-        <v>0.09799999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="I26">
-        <v>0.02667720625053031</v>
+        <v>0.02063879841463645</v>
       </c>
       <c r="J26">
-        <v>0.0007116733333333334</v>
+        <v>0.0004259599999999999</v>
       </c>
       <c r="K26">
-        <v>0.11</v>
+        <v>0.123</v>
       </c>
       <c r="L26">
-        <v>0.141</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1438,25 +1438,25 @@
         <v>17</v>
       </c>
       <c r="D28">
-        <v>0.20292</v>
+        <v>0.20668</v>
       </c>
       <c r="E28">
         <v>0.198</v>
       </c>
       <c r="F28">
-        <v>0.12</v>
+        <v>0.153</v>
       </c>
       <c r="G28">
         <v>0.279</v>
       </c>
       <c r="H28">
-        <v>0.159</v>
+        <v>0.126</v>
       </c>
       <c r="I28">
-        <v>0.03750324430410432</v>
+        <v>0.03121794355815258</v>
       </c>
       <c r="J28">
-        <v>0.001406493333333333</v>
+        <v>0.0009745600000000001</v>
       </c>
       <c r="K28">
         <v>0.19</v>
